--- a/Data/EXCEL/Transfer/bzPerformance/2024Q4/2071-bzPerformance-2024Q4.xlsx
+++ b/Data/EXCEL/Transfer/bzPerformance/2024Q4/2071-bzPerformance-2024Q4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\xls2xlsx\2024Q4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E7D934C1-07EA-4DDE-BE7E-E6DE7F3C9947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6166EB2A-9A57-4213-BF82-83C62A41BC73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1800" yWindow="840" windowWidth="17640" windowHeight="14310" xr2:uid="{C501779E-E170-4DE2-A334-67A814BA73BB}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{08A9D57B-5618-41E0-804B-5A933A653131}"/>
   </bookViews>
   <sheets>
     <sheet name="2071-bzPerformance-2024Q4" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="28">
   <si>
     <t>年度</t>
   </si>
@@ -104,19 +104,13 @@
   </si>
   <si>
     <t>-</t>
-  </si>
-  <si>
-    <t>24Q2</t>
-  </si>
-  <si>
-    <t>(年估)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -306,14 +300,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF008000"/>
-      <name val="新細明體"/>
-      <family val="1"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF808080"/>
       <name val="新細明體"/>
       <family val="1"/>
       <charset val="136"/>
@@ -861,7 +847,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -892,27 +878,21 @@
     <xf numFmtId="0" fontId="18" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -929,24 +909,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1323,20 +1285,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7023F2AD-A965-42F3-AD07-8A55047B9513}">
-  <dimension ref="A1:U13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CC4F4A2-7A47-41D1-BE8F-DEF906EADBE8}">
+  <dimension ref="A1:U12"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="3" width="7.08984375" customWidth="1"/>
-    <col min="4" max="4" width="7.453125" customWidth="1"/>
-    <col min="5" max="17" width="7.08984375" customWidth="1"/>
-    <col min="18" max="18" width="7.36328125" customWidth="1"/>
-    <col min="19" max="20" width="7.08984375" customWidth="1"/>
-    <col min="21" max="21" width="8.81640625" customWidth="1"/>
+    <col min="1" max="3" width="11.6328125" customWidth="1"/>
+    <col min="4" max="4" width="12.26953125" customWidth="1"/>
+    <col min="5" max="17" width="11.6328125" customWidth="1"/>
+    <col min="18" max="18" width="12.08984375" customWidth="1"/>
+    <col min="19" max="20" width="11.6328125" customWidth="1"/>
+    <col min="21" max="21" width="13.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -1345,54 +1307,54 @@
       <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="20" t="s">
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="20" t="s">
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="22"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="20"/>
       <c r="Q1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="R1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="S1" s="20" t="s">
+      <c r="S1" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="T1" s="22"/>
+      <c r="T1" s="20"/>
       <c r="U1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:21" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A2" s="18"/>
+      <c r="A2" s="16"/>
       <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="15" t="s">
         <v>16</v>
       </c>
       <c r="G2" s="2" t="s">
@@ -1442,12 +1404,12 @@
       </c>
     </row>
     <row r="3" spans="1:21" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A3" s="19"/>
+      <c r="A3" s="17"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
       <c r="G3" s="3" t="s">
         <v>9</v>
       </c>
@@ -1499,16 +1461,16 @@
         <v>27</v>
       </c>
       <c r="D4" s="7">
-        <v>22.6</v>
+        <v>22.75</v>
       </c>
       <c r="E4" s="7">
         <v>22.6</v>
       </c>
       <c r="F4" s="8">
-        <v>-0.9</v>
+        <v>-0.75</v>
       </c>
       <c r="G4" s="8">
-        <v>-3.8</v>
+        <v>-3.2</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>27</v>
@@ -1553,574 +1515,528 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:21" s="9" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="25">
+    <row r="5" spans="1:21" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+      <c r="A5" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B5" s="11">
+        <v>6.9</v>
+      </c>
+      <c r="C5" s="11">
+        <v>49</v>
+      </c>
+      <c r="D5" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="E5" s="11">
+        <v>27</v>
+      </c>
+      <c r="F5" s="12">
+        <v>-6.6</v>
+      </c>
+      <c r="G5" s="12">
+        <v>-21.9</v>
+      </c>
+      <c r="H5" s="11">
+        <v>15.9</v>
+      </c>
+      <c r="I5" s="11">
+        <v>2.86</v>
+      </c>
+      <c r="J5" s="11">
+        <v>1.74</v>
+      </c>
+      <c r="K5" s="11">
+        <v>0.05</v>
+      </c>
+      <c r="L5" s="11">
+        <v>1.43</v>
+      </c>
+      <c r="M5" s="11">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="N5" s="11">
+        <v>11</v>
+      </c>
+      <c r="O5" s="11">
+        <v>0.31</v>
+      </c>
+      <c r="P5" s="11">
+        <v>9.01</v>
+      </c>
+      <c r="Q5" s="11">
+        <v>10.6</v>
+      </c>
+      <c r="R5" s="11">
+        <v>5.65</v>
+      </c>
+      <c r="S5" s="11">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="T5" s="12">
+        <v>-0.21</v>
+      </c>
+      <c r="U5" s="11">
+        <v>20.399999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+      <c r="A6" s="6">
+        <v>2023</v>
+      </c>
+      <c r="B6" s="7">
         <v>6</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C6" s="7">
         <v>49</v>
       </c>
-      <c r="D5" s="25">
-        <v>23.5</v>
-      </c>
-      <c r="E5" s="25">
-        <v>27</v>
-      </c>
-      <c r="F5" s="27">
-        <v>-6.6</v>
-      </c>
-      <c r="G5" s="27">
-        <v>-21.9</v>
-      </c>
-      <c r="H5" s="25">
-        <v>7.5</v>
-      </c>
-      <c r="I5" s="25">
-        <v>1.29</v>
-      </c>
-      <c r="J5" s="25">
-        <v>0.75</v>
-      </c>
-      <c r="K5" s="25">
-        <v>0.08</v>
-      </c>
-      <c r="L5" s="25">
-        <v>0.67</v>
-      </c>
-      <c r="M5" s="25">
-        <v>17.2</v>
-      </c>
-      <c r="N5" s="25">
+      <c r="D6" s="7">
+        <v>30.1</v>
+      </c>
+      <c r="E6" s="7">
+        <v>34.4</v>
+      </c>
+      <c r="F6" s="13">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G6" s="13">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="H6" s="7">
+        <v>13.9</v>
+      </c>
+      <c r="I6" s="7">
+        <v>2.92</v>
+      </c>
+      <c r="J6" s="7">
+        <v>1.88</v>
+      </c>
+      <c r="K6" s="8">
+        <v>-0.16</v>
+      </c>
+      <c r="L6" s="7">
+        <v>1.32</v>
+      </c>
+      <c r="M6" s="7">
+        <v>21</v>
+      </c>
+      <c r="N6" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="O6" s="8">
+        <v>-1.1599999999999999</v>
+      </c>
+      <c r="P6" s="7">
+        <v>9.4600000000000009</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>11</v>
+      </c>
+      <c r="R6" s="7">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="S6" s="7">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="T6" s="8">
+        <v>-4.74</v>
+      </c>
+      <c r="U6" s="7">
+        <v>21.57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+      <c r="A7" s="10">
+        <v>2022</v>
+      </c>
+      <c r="B7" s="11">
+        <v>4.2</v>
+      </c>
+      <c r="C7" s="11">
+        <v>53</v>
+      </c>
+      <c r="D7" s="11">
+        <v>25.2</v>
+      </c>
+      <c r="E7" s="11">
+        <v>22.9</v>
+      </c>
+      <c r="F7" s="14">
+        <v>3.25</v>
+      </c>
+      <c r="G7" s="14">
+        <v>14.8</v>
+      </c>
+      <c r="H7" s="11">
+        <v>20.8</v>
+      </c>
+      <c r="I7" s="11">
+        <v>5.2</v>
+      </c>
+      <c r="J7" s="11">
+        <v>3.74</v>
+      </c>
+      <c r="K7" s="11">
+        <v>0</v>
+      </c>
+      <c r="L7" s="11">
+        <v>2.95</v>
+      </c>
+      <c r="M7" s="11">
+        <v>25</v>
+      </c>
+      <c r="N7" s="11">
+        <v>18</v>
+      </c>
+      <c r="O7" s="11">
+        <v>0.02</v>
+      </c>
+      <c r="P7" s="11">
+        <v>14.2</v>
+      </c>
+      <c r="Q7" s="11">
+        <v>30.2</v>
+      </c>
+      <c r="R7" s="11">
         <v>10</v>
       </c>
-      <c r="O5" s="25">
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="P5" s="25">
-        <v>8.9600000000000009</v>
-      </c>
-      <c r="Q5" s="10">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="R5" s="10">
-        <v>5.24</v>
-      </c>
-      <c r="S5" s="25">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="T5" s="27">
-        <v>-0.35</v>
-      </c>
-      <c r="U5" s="25">
-        <v>22.19</v>
+      <c r="S7" s="11">
+        <v>7.02</v>
+      </c>
+      <c r="T7" s="14">
+        <v>3.89</v>
+      </c>
+      <c r="U7" s="11">
+        <v>26.34</v>
       </c>
     </row>
-    <row r="6" spans="1:21" s="9" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="24"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="26"/>
-      <c r="M6" s="26"/>
-      <c r="N6" s="26"/>
-      <c r="O6" s="26"/>
-      <c r="P6" s="26"/>
-      <c r="Q6" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="R6" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="S6" s="26"/>
-      <c r="T6" s="28"/>
-      <c r="U6" s="26"/>
+    <row r="8" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+      <c r="A8" s="6">
+        <v>2021</v>
+      </c>
+      <c r="B8" s="7">
+        <v>4.2</v>
+      </c>
+      <c r="C8" s="7">
+        <v>43</v>
+      </c>
+      <c r="D8" s="7">
+        <v>21.95</v>
+      </c>
+      <c r="E8" s="7">
+        <v>22</v>
+      </c>
+      <c r="F8" s="8">
+        <v>-2.95</v>
+      </c>
+      <c r="G8" s="8">
+        <v>-11.8</v>
+      </c>
+      <c r="H8" s="7">
+        <v>18.2</v>
+      </c>
+      <c r="I8" s="7">
+        <v>2.91</v>
+      </c>
+      <c r="J8" s="7">
+        <v>1.39</v>
+      </c>
+      <c r="K8" s="7">
+        <v>0.16</v>
+      </c>
+      <c r="L8" s="7">
+        <v>1.31</v>
+      </c>
+      <c r="M8" s="7">
+        <v>16</v>
+      </c>
+      <c r="N8" s="7">
+        <v>7.64</v>
+      </c>
+      <c r="O8" s="7">
+        <v>0.85</v>
+      </c>
+      <c r="P8" s="7">
+        <v>7.23</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>16.8</v>
+      </c>
+      <c r="R8" s="7">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="S8" s="7">
+        <v>3.13</v>
+      </c>
+      <c r="T8" s="13">
+        <v>4.21</v>
+      </c>
+      <c r="U8" s="7">
+        <v>20.16</v>
+      </c>
     </row>
-    <row r="7" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A7" s="6">
-        <v>2023</v>
-      </c>
-      <c r="B7" s="7">
-        <v>6</v>
-      </c>
-      <c r="C7" s="7">
-        <v>49</v>
-      </c>
-      <c r="D7" s="7">
-        <v>30.1</v>
-      </c>
-      <c r="E7" s="7">
-        <v>34.4</v>
-      </c>
-      <c r="F7" s="12">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="G7" s="12">
-        <v>19.399999999999999</v>
-      </c>
-      <c r="H7" s="7">
-        <v>13.9</v>
-      </c>
-      <c r="I7" s="7">
-        <v>2.92</v>
-      </c>
-      <c r="J7" s="7">
-        <v>1.88</v>
-      </c>
-      <c r="K7" s="8">
-        <v>-0.16</v>
-      </c>
-      <c r="L7" s="7">
-        <v>1.32</v>
-      </c>
-      <c r="M7" s="7">
-        <v>21</v>
-      </c>
-      <c r="N7" s="7">
-        <v>13.5</v>
-      </c>
-      <c r="O7" s="8">
-        <v>-1.1599999999999999</v>
-      </c>
-      <c r="P7" s="7">
-        <v>9.4600000000000009</v>
-      </c>
-      <c r="Q7" s="7">
-        <v>11</v>
-      </c>
-      <c r="R7" s="7">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="S7" s="7">
-        <v>2.2799999999999998</v>
-      </c>
-      <c r="T7" s="8">
-        <v>-4.74</v>
-      </c>
-      <c r="U7" s="7">
-        <v>21.57</v>
+    <row r="9" spans="1:21" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+      <c r="A9" s="10">
+        <v>2020</v>
+      </c>
+      <c r="B9" s="11">
+        <v>4.2</v>
+      </c>
+      <c r="C9" s="12">
+        <v>26</v>
+      </c>
+      <c r="D9" s="11">
+        <v>24.9</v>
+      </c>
+      <c r="E9" s="11">
+        <v>23</v>
+      </c>
+      <c r="F9" s="12">
+        <v>-3.4</v>
+      </c>
+      <c r="G9" s="12">
+        <v>-12</v>
+      </c>
+      <c r="H9" s="11">
+        <v>18.3</v>
+      </c>
+      <c r="I9" s="11">
+        <v>1.33</v>
+      </c>
+      <c r="J9" s="11">
+        <v>0.09</v>
+      </c>
+      <c r="K9" s="12">
+        <v>-0.68</v>
+      </c>
+      <c r="L9" s="12">
+        <v>-0.45</v>
+      </c>
+      <c r="M9" s="11">
+        <v>7.27</v>
+      </c>
+      <c r="N9" s="11">
+        <v>0.48</v>
+      </c>
+      <c r="O9" s="12">
+        <v>-3.71</v>
+      </c>
+      <c r="P9" s="12">
+        <v>-2.48</v>
+      </c>
+      <c r="Q9" s="12">
+        <v>-6.14</v>
+      </c>
+      <c r="R9" s="12">
+        <v>-1.65</v>
+      </c>
+      <c r="S9" s="12">
+        <v>-1.08</v>
+      </c>
+      <c r="T9" s="12">
+        <v>-0.96</v>
+      </c>
+      <c r="U9" s="11">
+        <v>17.04</v>
       </c>
     </row>
-    <row r="8" spans="1:21" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A8" s="13">
-        <v>2022</v>
-      </c>
-      <c r="B8" s="14">
+    <row r="10" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+      <c r="A10" s="6">
+        <v>2019</v>
+      </c>
+      <c r="B10" s="7">
         <v>4.2</v>
       </c>
-      <c r="C8" s="14">
-        <v>53</v>
-      </c>
-      <c r="D8" s="14">
-        <v>25.2</v>
-      </c>
-      <c r="E8" s="14">
-        <v>22.9</v>
-      </c>
-      <c r="F8" s="15">
-        <v>3.25</v>
-      </c>
-      <c r="G8" s="15">
-        <v>14.8</v>
-      </c>
-      <c r="H8" s="14">
-        <v>20.8</v>
-      </c>
-      <c r="I8" s="14">
-        <v>5.2</v>
-      </c>
-      <c r="J8" s="14">
-        <v>3.74</v>
-      </c>
-      <c r="K8" s="14">
-        <v>0</v>
-      </c>
-      <c r="L8" s="14">
-        <v>2.95</v>
-      </c>
-      <c r="M8" s="14">
-        <v>25</v>
-      </c>
-      <c r="N8" s="14">
-        <v>18</v>
-      </c>
-      <c r="O8" s="14">
-        <v>0.02</v>
-      </c>
-      <c r="P8" s="14">
+      <c r="C10" s="8">
+        <v>30</v>
+      </c>
+      <c r="D10" s="7">
+        <v>28.3</v>
+      </c>
+      <c r="E10" s="7">
+        <v>28.9</v>
+      </c>
+      <c r="F10" s="8">
+        <v>-1.29</v>
+      </c>
+      <c r="G10" s="8">
+        <v>-4.4000000000000004</v>
+      </c>
+      <c r="H10" s="7">
+        <v>15.8</v>
+      </c>
+      <c r="I10" s="7">
+        <v>1.43</v>
+      </c>
+      <c r="J10" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="K10" s="8">
+        <v>-0.31</v>
+      </c>
+      <c r="L10" s="8">
+        <v>-0.05</v>
+      </c>
+      <c r="M10" s="7">
+        <v>9</v>
+      </c>
+      <c r="N10" s="7">
+        <v>1.58</v>
+      </c>
+      <c r="O10" s="8">
+        <v>-1.95</v>
+      </c>
+      <c r="P10" s="8">
+        <v>-0.31</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>-0.66</v>
+      </c>
+      <c r="R10" s="8">
+        <v>-0.18</v>
+      </c>
+      <c r="S10" s="8">
+        <v>-0.12</v>
+      </c>
+      <c r="T10" s="8">
+        <v>-2.5099999999999998</v>
+      </c>
+      <c r="U10" s="7">
+        <v>18.12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+      <c r="A11" s="10">
+        <v>2018</v>
+      </c>
+      <c r="B11" s="11">
+        <v>4.05</v>
+      </c>
+      <c r="C11" s="11">
+        <v>40</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="11">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="I11" s="11">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="J11" s="11">
+        <v>0.8</v>
+      </c>
+      <c r="K11" s="11">
+        <v>0.33</v>
+      </c>
+      <c r="L11" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="M11" s="11">
+        <v>13.1</v>
+      </c>
+      <c r="N11" s="11">
+        <v>4.2</v>
+      </c>
+      <c r="O11" s="11">
+        <v>1.75</v>
+      </c>
+      <c r="P11" s="11">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="Q11" s="11">
         <v>14.2</v>
       </c>
-      <c r="Q8" s="14">
-        <v>30.2</v>
-      </c>
-      <c r="R8" s="14">
-        <v>10</v>
-      </c>
-      <c r="S8" s="14">
-        <v>7.02</v>
-      </c>
-      <c r="T8" s="15">
-        <v>3.89</v>
-      </c>
-      <c r="U8" s="14">
-        <v>26.34</v>
+      <c r="R11" s="11">
+        <v>3.45</v>
+      </c>
+      <c r="S11" s="11">
+        <v>2.39</v>
+      </c>
+      <c r="T11" s="14">
+        <v>1.81</v>
+      </c>
+      <c r="U11" s="11">
+        <v>18.5</v>
       </c>
     </row>
-    <row r="9" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A9" s="6">
-        <v>2021</v>
-      </c>
-      <c r="B9" s="7">
-        <v>4.2</v>
-      </c>
-      <c r="C9" s="7">
-        <v>43</v>
-      </c>
-      <c r="D9" s="7">
-        <v>21.95</v>
-      </c>
-      <c r="E9" s="7">
-        <v>22</v>
-      </c>
-      <c r="F9" s="8">
-        <v>-2.95</v>
-      </c>
-      <c r="G9" s="8">
-        <v>-11.8</v>
-      </c>
-      <c r="H9" s="7">
-        <v>18.2</v>
-      </c>
-      <c r="I9" s="7">
-        <v>2.91</v>
-      </c>
-      <c r="J9" s="7">
-        <v>1.39</v>
-      </c>
-      <c r="K9" s="7">
-        <v>0.16</v>
-      </c>
-      <c r="L9" s="7">
-        <v>1.31</v>
-      </c>
-      <c r="M9" s="7">
-        <v>16</v>
-      </c>
-      <c r="N9" s="7">
-        <v>7.64</v>
-      </c>
-      <c r="O9" s="7">
-        <v>0.85</v>
-      </c>
-      <c r="P9" s="7">
-        <v>7.23</v>
-      </c>
-      <c r="Q9" s="7">
-        <v>16.8</v>
-      </c>
-      <c r="R9" s="7">
-        <v>4.4400000000000004</v>
-      </c>
-      <c r="S9" s="7">
-        <v>3.13</v>
-      </c>
-      <c r="T9" s="12">
-        <v>4.21</v>
-      </c>
-      <c r="U9" s="7">
-        <v>20.16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A10" s="13">
-        <v>2020</v>
-      </c>
-      <c r="B10" s="14">
-        <v>4.2</v>
-      </c>
-      <c r="C10" s="16">
-        <v>26</v>
-      </c>
-      <c r="D10" s="14">
-        <v>24.9</v>
-      </c>
-      <c r="E10" s="14">
-        <v>23</v>
-      </c>
-      <c r="F10" s="16">
-        <v>-3.4</v>
-      </c>
-      <c r="G10" s="16">
-        <v>-12</v>
-      </c>
-      <c r="H10" s="14">
+    <row r="12" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
+      <c r="A12" s="6">
+        <v>2017</v>
+      </c>
+      <c r="B12" s="7">
+        <v>3.45</v>
+      </c>
+      <c r="C12" s="8">
+        <v>34</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="7">
         <v>18.3</v>
       </c>
-      <c r="I10" s="14">
-        <v>1.33</v>
-      </c>
-      <c r="J10" s="14">
-        <v>0.09</v>
-      </c>
-      <c r="K10" s="16">
-        <v>-0.68</v>
-      </c>
-      <c r="L10" s="16">
-        <v>-0.45</v>
-      </c>
-      <c r="M10" s="14">
-        <v>7.27</v>
-      </c>
-      <c r="N10" s="14">
-        <v>0.48</v>
-      </c>
-      <c r="O10" s="16">
-        <v>-3.71</v>
-      </c>
-      <c r="P10" s="16">
-        <v>-2.48</v>
-      </c>
-      <c r="Q10" s="16">
-        <v>-6.14</v>
-      </c>
-      <c r="R10" s="16">
-        <v>-1.65</v>
-      </c>
-      <c r="S10" s="16">
-        <v>-1.08</v>
-      </c>
-      <c r="T10" s="16">
-        <v>-0.96</v>
-      </c>
-      <c r="U10" s="14">
-        <v>17.04</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A11" s="6">
-        <v>2019</v>
-      </c>
-      <c r="B11" s="7">
-        <v>4.2</v>
-      </c>
-      <c r="C11" s="8">
-        <v>30</v>
-      </c>
-      <c r="D11" s="7">
-        <v>28.3</v>
-      </c>
-      <c r="E11" s="7">
-        <v>28.9</v>
-      </c>
-      <c r="F11" s="8">
-        <v>-1.29</v>
-      </c>
-      <c r="G11" s="8">
-        <v>-4.4000000000000004</v>
-      </c>
-      <c r="H11" s="7">
-        <v>15.8</v>
-      </c>
-      <c r="I11" s="7">
-        <v>1.43</v>
-      </c>
-      <c r="J11" s="7">
-        <v>0.25</v>
-      </c>
-      <c r="K11" s="8">
-        <v>-0.31</v>
-      </c>
-      <c r="L11" s="8">
-        <v>-0.05</v>
-      </c>
-      <c r="M11" s="7">
-        <v>9</v>
-      </c>
-      <c r="N11" s="7">
-        <v>1.58</v>
-      </c>
-      <c r="O11" s="8">
-        <v>-1.95</v>
-      </c>
-      <c r="P11" s="8">
-        <v>-0.31</v>
-      </c>
-      <c r="Q11" s="8">
-        <v>-0.66</v>
-      </c>
-      <c r="R11" s="8">
-        <v>-0.18</v>
-      </c>
-      <c r="S11" s="8">
-        <v>-0.12</v>
-      </c>
-      <c r="T11" s="8">
-        <v>-2.5099999999999998</v>
-      </c>
-      <c r="U11" s="7">
-        <v>18.12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A12" s="13">
-        <v>2018</v>
-      </c>
-      <c r="B12" s="14">
-        <v>4.05</v>
-      </c>
-      <c r="C12" s="14">
-        <v>40</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="H12" s="14">
-        <v>18.899999999999999</v>
-      </c>
-      <c r="I12" s="14">
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="J12" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="K12" s="14">
-        <v>0.33</v>
-      </c>
-      <c r="L12" s="14">
-        <v>0.9</v>
-      </c>
-      <c r="M12" s="14">
-        <v>13.1</v>
-      </c>
-      <c r="N12" s="14">
-        <v>4.2</v>
-      </c>
-      <c r="O12" s="14">
-        <v>1.75</v>
-      </c>
-      <c r="P12" s="14">
-        <v>4.7300000000000004</v>
-      </c>
-      <c r="Q12" s="14">
-        <v>14.2</v>
-      </c>
-      <c r="R12" s="14">
-        <v>3.45</v>
-      </c>
-      <c r="S12" s="14">
-        <v>2.39</v>
-      </c>
-      <c r="T12" s="15">
-        <v>1.81</v>
-      </c>
-      <c r="U12" s="14">
-        <v>18.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A13" s="6">
-        <v>2017</v>
-      </c>
-      <c r="B13" s="7">
-        <v>3.45</v>
-      </c>
-      <c r="C13" s="8">
-        <v>34</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H13" s="7">
-        <v>18.3</v>
-      </c>
-      <c r="I13" s="7">
+      <c r="I12" s="7">
         <v>2.2400000000000002</v>
       </c>
-      <c r="J13" s="7">
+      <c r="J12" s="7">
         <v>0.88</v>
       </c>
-      <c r="K13" s="8">
+      <c r="K12" s="8">
         <v>-0.61</v>
       </c>
-      <c r="L13" s="7">
+      <c r="L12" s="7">
         <v>0.2</v>
       </c>
-      <c r="M13" s="7">
+      <c r="M12" s="7">
         <v>12.3</v>
       </c>
-      <c r="N13" s="7">
+      <c r="N12" s="7">
         <v>4.8099999999999996</v>
       </c>
-      <c r="O13" s="8">
+      <c r="O12" s="8">
         <v>-3.32</v>
       </c>
-      <c r="P13" s="7">
+      <c r="P12" s="7">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Q13" s="7">
+      <c r="Q12" s="7">
         <v>3.94</v>
       </c>
-      <c r="R13" s="7">
+      <c r="R12" s="7">
         <v>0.86</v>
       </c>
-      <c r="S13" s="7">
+      <c r="S12" s="7">
         <v>0.57999999999999996</v>
       </c>
-      <c r="T13" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="U13" s="6" t="s">
+      <c r="T12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="U12" s="6" t="s">
         <v>27</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="27">
-    <mergeCell ref="U5:U6"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="O5:O6"/>
-    <mergeCell ref="P5:P6"/>
-    <mergeCell ref="S5:S6"/>
-    <mergeCell ref="T5:T6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
+  <mergeCells count="8">
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="D1:G1"/>
     <mergeCell ref="H1:L1"/>
@@ -2130,7 +2046,7 @@
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="F2:F3"/>
   </mergeCells>
-  <phoneticPr fontId="25" type="noConversion"/>
+  <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>